--- a/history_matching/example/iter2/Cuts/RadiusShouldBe15/train_data.xlsx
+++ b/history_matching/example/iter2/Cuts/RadiusShouldBe15/train_data.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
   <si>
     <t>Sample_Id</t>
   </si>
@@ -67,124 +68,127 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Data_20170712_104006.000000</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000001</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000002</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000003</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000004</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000005</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000006</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000007</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000008</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000009</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000010</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000011</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000012</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000013</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000014</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000015</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000016</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000017</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000018</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000019</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000020</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000021</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000022</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000023</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000024</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000025</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000026</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000027</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000028</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000029</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000030</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000031</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000032</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000033</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000034</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000035</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000036</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000037</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000038</t>
+    <t>Data_20180119_074635.000000</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000001</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000002</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000003</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000004</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000005</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000006</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000007</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000008</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000009</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000010</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000011</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000012</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000013</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000014</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000015</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000016</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000017</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000018</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000019</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000020</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000021</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000022</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000023</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000024</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000025</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000026</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000027</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000028</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000029</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000030</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000031</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000032</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000033</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000034</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000035</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000036</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000037</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000038</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000039</t>
   </si>
 </sst>
 </file>
@@ -533,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -600,46 +604,46 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.405137365595422</v>
+        <v>-12.14684535151868</v>
       </c>
       <c r="E2" t="n">
-        <v>-11.8830846696643</v>
+        <v>-19.8468228003866</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>12.07768264651286</v>
+        <v>23.6679788130077</v>
       </c>
       <c r="H2" t="n">
-        <v>12.25561154535399</v>
+        <v>24.18631516111157</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1779288988411256</v>
+        <v>-0.5183363481038654</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002947665365159297</v>
+        <v>5.994731403539465e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>12.2559063118905</v>
+        <v>24.18632115584297</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2078223527434</v>
+        <v>2.091623860877034</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0278753973543644</v>
+        <v>1.710048534137996e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.475698365126505</v>
+        <v>4.408750548265395</v>
       </c>
       <c r="O2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1621675068137054</v>
+        <v>-0.3584056881250401</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.067467918890569</v>
+        <v>-125.346574236864</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -653,46 +657,46 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-10.40425993869515</v>
+        <v>4.904898148493372</v>
       </c>
       <c r="E3" t="n">
-        <v>-9.476311445201773</v>
+        <v>1.967001998453881</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>15.03290066092008</v>
+        <v>4.638463146816595</v>
       </c>
       <c r="H3" t="n">
-        <v>13.25884486609738</v>
+        <v>6.982382181683306</v>
       </c>
       <c r="I3" t="n">
-        <v>1.774055794822702</v>
+        <v>-2.343919034866711</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00109519321345556</v>
+        <v>-1.680816142548275e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>13.25994005931083</v>
+        <v>6.982365373521881</v>
       </c>
       <c r="L3" t="n">
-        <v>1.209648385085073</v>
+        <v>2.091623861076854</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02970143035054207</v>
+        <v>1.710068516150588e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9355095552683187</v>
+        <v>3.847867982710427</v>
       </c>
       <c r="O3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1.612016600745307</v>
+        <v>-1.620681586275447</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.28751285952408</v>
+        <v>-566.8037774731993</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -706,46 +710,46 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>-20.7857936424723</v>
+        <v>10.17802948191527</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.232261528089538</v>
+        <v>-6.083306211143764</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>19.50707810120585</v>
+        <v>11.36908837759391</v>
       </c>
       <c r="H4" t="n">
-        <v>21.77033768067582</v>
+        <v>11.41550916961251</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.263259579469974</v>
+        <v>-0.04642079201859595</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002461325259139695</v>
+        <v>1.905459446655853e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>21.77279900593496</v>
+        <v>11.41552822420697</v>
       </c>
       <c r="L4" t="n">
-        <v>1.218398181504376</v>
+        <v>2.091623860740872</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03845122456550598</v>
+        <v>1.71003491792033e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.636668480367687</v>
+        <v>1.720279711423503</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.052635287091111</v>
+        <v>-0.03211064157189088</v>
       </c>
       <c r="Q4" t="n">
-        <v>-11.55450468186865</v>
+        <v>-11.23022059979408</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -759,46 +763,46 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.227042732383623</v>
+        <v>-6.753743942882013</v>
       </c>
       <c r="E5" t="n">
-        <v>5.846666045038035</v>
+        <v>-22.76013445207743</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>10.23734299679114</v>
+        <v>23.87432497126383</v>
       </c>
       <c r="H5" t="n">
-        <v>9.113492715366021</v>
+        <v>24.35860916701603</v>
       </c>
       <c r="I5" t="n">
-        <v>1.123850281425119</v>
+        <v>-0.4842841957521955</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0009729532020457688</v>
+        <v>1.303124534510539e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>9.112519762163975</v>
+        <v>24.35862219826137</v>
       </c>
       <c r="L5" t="n">
-        <v>1.207356403964824</v>
+        <v>2.091623860987496</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02740944921970367</v>
+        <v>1.710059580287055e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.166338828494941</v>
+        <v>4.491442226666035</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1.023685457329996</v>
+        <v>-0.3348653323305325</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.794134174235575</v>
+        <v>-117.1133384972587</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -812,46 +816,46 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-13.20516413704294</v>
+        <v>-5.189547005439286</v>
       </c>
       <c r="E6" t="n">
-        <v>1.261663540521198</v>
+        <v>-15.99828556386437</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>11.17708987639076</v>
+        <v>18.33645025779595</v>
       </c>
       <c r="H6" t="n">
-        <v>12.59141873627198</v>
+        <v>15.4187273154717</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.414328859881216</v>
+        <v>2.91772294232425</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0016928845996102</v>
+        <v>3.836161909712691e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>12.59311162087159</v>
+        <v>15.41873115163361</v>
       </c>
       <c r="L6" t="n">
-        <v>1.21066512109883</v>
+        <v>2.091623860901448</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03071816638112068</v>
+        <v>1.710050975482342e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.293826857747414</v>
+        <v>0.2009597926108949</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.286938836893003</v>
+        <v>2.017444915407818</v>
       </c>
       <c r="Q6" t="n">
-        <v>-8.079273126972121</v>
+        <v>705.5681221776304</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -865,46 +869,46 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4.148377553764135</v>
+        <v>-1.256059070692373</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56232694657282</v>
+        <v>-18.05910606199234</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>17.48497064794596</v>
+        <v>18.28885081839581</v>
       </c>
       <c r="H7" t="n">
-        <v>17.11295935712576</v>
+        <v>16.80867044993374</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3720112908202005</v>
+        <v>1.480180368462069</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0004219626030882528</v>
+        <v>-1.988268075029135e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>17.11253739452267</v>
+        <v>16.80865056725299</v>
       </c>
       <c r="L7" t="n">
-        <v>1.208988719087241</v>
+        <v>2.091623861080364</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02904176339507103</v>
+        <v>1.710068867076339e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.135873146588003</v>
+        <v>0.8680176802591572</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3387172592690217</v>
+        <v>1.023478395853361</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.185430252511924</v>
+        <v>357.9428348678881</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -918,46 +922,46 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08906562902339488</v>
+        <v>-13.54903056732685</v>
       </c>
       <c r="E8" t="n">
-        <v>-17.5373498725817</v>
+        <v>-17.39727569829309</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>16.49864117001303</v>
+        <v>21.27033667140947</v>
       </c>
       <c r="H8" t="n">
-        <v>16.78598493628473</v>
+        <v>22.72845973801782</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2873437662717038</v>
+        <v>-1.458123066608348</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0006449034869460787</v>
+        <v>1.334704803621574e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>16.78534003279779</v>
+        <v>22.72846107272262</v>
       </c>
       <c r="L8" t="n">
-        <v>1.208768717800043</v>
+        <v>2.091623860897471</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02882176265120506</v>
+        <v>1.710050577809922e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9599755724008997</v>
+        <v>3.709086196040661</v>
       </c>
       <c r="O8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2607680408663972</v>
+        <v>-1.008214140028465</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.688751320899287</v>
+        <v>-352.6063263552313</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -971,46 +975,46 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.70434314501162</v>
+        <v>13.89487980954055</v>
       </c>
       <c r="E9" t="n">
-        <v>7.343673720746779</v>
+        <v>-17.70422085822753</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>11.29734640870898</v>
+        <v>23.1140571947468</v>
       </c>
       <c r="H9" t="n">
-        <v>10.1570263059574</v>
+        <v>24.54498118531205</v>
       </c>
       <c r="I9" t="n">
-        <v>1.140320102751579</v>
+        <v>-1.430923990565255</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009220338013293973</v>
+        <v>1.270842902554682e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>10.15794833975873</v>
+        <v>24.54499389374108</v>
       </c>
       <c r="L9" t="n">
-        <v>1.207244155227742</v>
+        <v>2.091623860938371</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02729720063507557</v>
+        <v>1.710054667819738e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.60414038781711</v>
+        <v>4.580886771540488</v>
       </c>
       <c r="O9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.036998010866751</v>
+        <v>-0.9894153147003982</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.896304140129144</v>
+        <v>-346.031332332813</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1024,46 +1028,46 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.634246567182217</v>
+        <v>-10.32818271504884</v>
       </c>
       <c r="E10" t="n">
-        <v>-17.98590593535273</v>
+        <v>9.479599790308342</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>20.81144277573021</v>
+        <v>14.97282186755557</v>
       </c>
       <c r="H10" t="n">
-        <v>20.08380166165975</v>
+        <v>13.77143818484581</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7276411140704617</v>
+        <v>1.201383682709764</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0006478472921885936</v>
+        <v>1.947224135134614e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>20.08444950895194</v>
+        <v>13.77145765708716</v>
       </c>
       <c r="L10" t="n">
-        <v>1.211027059818177</v>
+        <v>2.091623860615918</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03108010441064835</v>
+        <v>1.710022422562927e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.733011389276221</v>
+        <v>0.5896089017747932</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6606226577865614</v>
+        <v>0.8306783586565727</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.123719836245232</v>
+        <v>290.5184960873896</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1077,46 +1081,46 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9179955011884928</v>
+        <v>-10.55346123029825</v>
       </c>
       <c r="E11" t="n">
-        <v>8.221877705926815</v>
+        <v>8.020785170490411</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>7.362065924250714</v>
+        <v>13.82482571323672</v>
       </c>
       <c r="H11" t="n">
-        <v>9.149038174035752</v>
+        <v>13.12015753563014</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.786972249785038</v>
+        <v>0.7046681776065782</v>
       </c>
       <c r="J11" t="n">
-        <v>9.624576747378961e-05</v>
+        <v>1.926403017697167e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>9.149134419803225</v>
+        <v>13.12017679966032</v>
       </c>
       <c r="L11" t="n">
-        <v>1.206174409256262</v>
+        <v>2.091623860596933</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02622745372354984</v>
+        <v>1.710020523995167e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.147185165448672</v>
+        <v>0.9021752478287283</v>
       </c>
       <c r="O11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.627182045801195</v>
+        <v>0.487226602774537</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11.03476641473167</v>
+        <v>170.4009945532094</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1130,46 +1134,46 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5221679191191271</v>
+        <v>16.04255249472128</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.52744229607183</v>
+        <v>2.290772923465952</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>19.72869517164893</v>
+        <v>17.9863059862221</v>
       </c>
       <c r="H12" t="n">
-        <v>20.69456810837579</v>
+        <v>15.7305606089717</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9658729367268606</v>
+        <v>2.255745377250399</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0006487110814781908</v>
+        <v>2.999809046257173e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>20.69391939729431</v>
+        <v>15.73059060706216</v>
       </c>
       <c r="L12" t="n">
-        <v>1.209918355556147</v>
+        <v>2.091623860714704</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02997140027582645</v>
+        <v>1.710032301135204e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.061106148138896</v>
+        <v>0.3506291239833654</v>
       </c>
       <c r="O12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.877506174021475</v>
+        <v>1.559705152180395</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.575383045072892</v>
+        <v>545.4841595779037</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1183,46 +1187,46 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.869572360546456</v>
+        <v>-7.086487760559926</v>
       </c>
       <c r="E13" t="n">
-        <v>14.00225299729911</v>
+        <v>4.035577394917353</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>12.89690699718333</v>
+        <v>8.425747810866286</v>
       </c>
       <c r="H13" t="n">
-        <v>14.01955073659639</v>
+        <v>8.910522948238849</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.122643739413057</v>
+        <v>-0.4847751373725639</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0005161285377046709</v>
+        <v>1.042458375546595e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>14.02006686513409</v>
+        <v>8.910533372822606</v>
       </c>
       <c r="L13" t="n">
-        <v>1.207618629558925</v>
+        <v>2.091623860732208</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02767167426645756</v>
+        <v>1.710034051471049e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5269967029335677</v>
+        <v>2.922490829158952</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.022060666635876</v>
+        <v>-0.3352029895564081</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.751866548223274</v>
+        <v>-117.2323033059687</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1236,46 +1240,46 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>19.5037380693124</v>
+        <v>16.74046363332193</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.969874668134551</v>
+        <v>-4.305734760551586</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>21.61305145446846</v>
+        <v>17.07676913234558</v>
       </c>
       <c r="H14" t="n">
-        <v>21.2303546605898</v>
+        <v>17.57919334559887</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3826967938786652</v>
+        <v>-0.5024242132532883</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.002598949260595086</v>
+        <v>1.978167615422617e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>21.2277557113292</v>
+        <v>17.57921312727502</v>
       </c>
       <c r="L14" t="n">
-        <v>1.218513618289252</v>
+        <v>2.091623860854852</v>
       </c>
       <c r="M14" t="n">
-        <v>0.03856666386127472</v>
+        <v>1.710046315894872e-05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.343950705347128</v>
+        <v>1.237830367139244</v>
       </c>
       <c r="O14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3490430678783866</v>
+        <v>-0.3474128406391181</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.961951105641203</v>
+        <v>-121.5020829937273</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1289,46 +1293,46 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>6.650452359280791</v>
+        <v>-5.938798193498763</v>
       </c>
       <c r="E15" t="n">
-        <v>-18.94785095803532</v>
+        <v>9.907537890770882</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>18.44837706303902</v>
+        <v>11.80558237977359</v>
       </c>
       <c r="H15" t="n">
-        <v>19.77404198681714</v>
+        <v>10.92210091302934</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.32566492377812</v>
+        <v>0.8834814667442501</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.001612799621922258</v>
+        <v>1.592090989748252e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>19.77242918719521</v>
+        <v>10.92210250512033</v>
       </c>
       <c r="L15" t="n">
-        <v>1.210854515394585</v>
+        <v>2.091623860891521</v>
       </c>
       <c r="M15" t="n">
-        <v>0.03090756013989449</v>
+        <v>1.710049982868096e-05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.565357062686095</v>
+        <v>1.957087337933492</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.203258946825604</v>
+        <v>0.6108785376988971</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.531347951972736</v>
+        <v>213.6447664685717</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1342,46 +1346,46 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>8.819047718307928</v>
+        <v>12.83422828743795</v>
       </c>
       <c r="E16" t="n">
-        <v>3.819299600338695</v>
+        <v>-9.557348754083264</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>9.053189011497579</v>
+        <v>16.47772549903024</v>
       </c>
       <c r="H16" t="n">
-        <v>9.626410278675849</v>
+        <v>15.76609441820932</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.573221267178269</v>
+        <v>0.7116310808209185</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.001354445611738213</v>
+        <v>2.44558936171368e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>9.62505583306411</v>
+        <v>15.76611887410294</v>
       </c>
       <c r="L16" t="n">
-        <v>1.208506760764316</v>
+        <v>2.091623860706821</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02855980582535267</v>
+        <v>1.710031512819588e-05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.890211620331938</v>
+        <v>0.3676800483026509</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5202000125276734</v>
+        <v>0.4920374837539334</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.383898064282886</v>
+        <v>172.0829829893228</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1395,46 +1399,46 @@
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-16.40687471406214</v>
+        <v>11.8019786398993</v>
       </c>
       <c r="E17" t="n">
-        <v>14.95889613445267</v>
+        <v>-6.702548910423928</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>22.69802128737657</v>
+        <v>13.54125036596258</v>
       </c>
       <c r="H17" t="n">
-        <v>23.65502989239121</v>
+        <v>13.09930685887457</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9570086050146429</v>
+        <v>0.4419435070880091</v>
       </c>
       <c r="J17" t="n">
-        <v>0.002280421813335952</v>
+        <v>2.548479129295552e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>23.65731031420455</v>
+        <v>13.09933234366586</v>
       </c>
       <c r="L17" t="n">
-        <v>1.21544473244624</v>
+        <v>2.091623860679615</v>
       </c>
       <c r="M17" t="n">
-        <v>0.03549777716398239</v>
+        <v>1.710028792246219e-05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.650541199884718</v>
+        <v>0.912179035542875</v>
       </c>
       <c r="O17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8701254447773542</v>
+        <v>0.3055624049874738</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.09153689875896</v>
+        <v>106.8661102115522</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1448,46 +1452,46 @@
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>5.719586926414387</v>
+        <v>-15.27406783503279</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.628332975108989</v>
+        <v>2.761848113869746</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>8.7475153982141</v>
+        <v>15.65036225985333</v>
       </c>
       <c r="H18" t="n">
-        <v>8.85145207304987</v>
+        <v>16.16947542351056</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1039366748357704</v>
+        <v>-0.5191131636572326</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.001211743626382865</v>
+        <v>2.642062974713986e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>8.850240329423487</v>
+        <v>16.16947568771686</v>
       </c>
       <c r="L18" t="n">
-        <v>1.207273090226727</v>
+        <v>2.091623860909556</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02732613496482372</v>
+        <v>1.710051786312976e-05</v>
       </c>
       <c r="N18" t="n">
-        <v>3.307434872759854</v>
+        <v>0.5612613027475101</v>
       </c>
       <c r="O18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.09349170905613836</v>
+        <v>-0.3589388517041497</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.6214222043284876</v>
+        <v>-125.5329201796075</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1501,46 +1505,46 @@
         <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>-10.01269538054338</v>
+        <v>-4.834730488292834</v>
       </c>
       <c r="E19" t="n">
-        <v>7.837745334597315</v>
+        <v>-23.01933872568203</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>13.35440912475893</v>
+        <v>23.88169107131525</v>
       </c>
       <c r="H19" t="n">
-        <v>12.28475826702248</v>
+        <v>23.97807877521501</v>
       </c>
       <c r="I19" t="n">
-        <v>1.069650857736448</v>
+        <v>-0.09638770389976159</v>
       </c>
       <c r="J19" t="n">
-        <v>0.001394690159446576</v>
+        <v>5.50018338588372e-06</v>
       </c>
       <c r="K19" t="n">
-        <v>12.28615295718193</v>
+        <v>23.97808427539839</v>
       </c>
       <c r="L19" t="n">
-        <v>1.208967511638882</v>
+        <v>2.091623860992053</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02902055718004704</v>
+        <v>1.71006003592802e-05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.459190941547673</v>
+        <v>4.308812341688603</v>
       </c>
       <c r="O19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9715565717367891</v>
+        <v>-0.06665068581909565</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.27079378817469</v>
+        <v>-23.30991755756904</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1554,46 +1558,46 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>19.25515532885564</v>
+        <v>9.996879782450131</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.743097604737869</v>
+        <v>-21.96991246467039</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>21.23450251709688</v>
+        <v>25.35433114066483</v>
       </c>
       <c r="H20" t="n">
-        <v>20.25975412774648</v>
+        <v>26.35047027572301</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9747483893504061</v>
+        <v>-0.9961391350581827</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.002564016444236602</v>
+        <v>7.542495059044594e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>20.25719011130224</v>
+        <v>26.35047781821807</v>
       </c>
       <c r="L20" t="n">
-        <v>1.218055059197543</v>
+        <v>2.091623861029304</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03810810297727585</v>
+        <v>1.710063761129189e-05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.82299877989217</v>
+        <v>5.447384698872269</v>
       </c>
       <c r="O20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8855232159517036</v>
+        <v>-0.6887815366887949</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.006390610418123</v>
+        <v>-240.8890943976903</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1607,46 +1611,46 @@
         <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>10.73057165210123</v>
+        <v>-11.06057874938554</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8031920278743598</v>
+        <v>1.579680160257112</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>10.45077554890572</v>
+        <v>10.93484895637239</v>
       </c>
       <c r="H21" t="n">
-        <v>10.18337447889775</v>
+        <v>11.42697149372634</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2674010700079723</v>
+        <v>-0.4921225373539517</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.001690262380552772</v>
+        <v>1.75090435585368e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>10.18168421651719</v>
+        <v>11.4269890027699</v>
       </c>
       <c r="L21" t="n">
-        <v>1.209616755839175</v>
+        <v>2.091623860555178</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02966980077326298</v>
+        <v>1.710016348456636e-05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.590486083483697</v>
+        <v>1.714779390611766</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.244667233871654</v>
+        <v>-0.3402882176897832</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.562220699654363</v>
+        <v>-119.0114028935219</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1660,46 +1664,46 @@
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>7.977089495017879</v>
+        <v>-12.89647450282712</v>
       </c>
       <c r="E22" t="n">
-        <v>10.37880305918925</v>
+        <v>-11.43055333189162</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>13.93918512099685</v>
+        <v>17.68689301346062</v>
       </c>
       <c r="H22" t="n">
-        <v>12.63928350213126</v>
+        <v>16.82353441609195</v>
       </c>
       <c r="I22" t="n">
-        <v>1.299901618865587</v>
+        <v>0.8633585973686735</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.001086045155581834</v>
+        <v>5.869554426150801e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>12.63819745697568</v>
+        <v>16.82354028564637</v>
       </c>
       <c r="L22" t="n">
-        <v>1.208957791558385</v>
+        <v>2.091623860734678</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0290108360350132</v>
+        <v>1.710034298441449e-05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.269904185612428</v>
+        <v>0.8751636370938022</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.183225741470242</v>
+        <v>0.5969617045462264</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.638235479527138</v>
+        <v>208.778539381257</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1713,46 +1717,46 @@
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>7.493755896275346</v>
+        <v>8.044677671473679</v>
       </c>
       <c r="E23" t="n">
-        <v>16.1361602703834</v>
+        <v>22.96478865975635</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>18.36928911764458</v>
+        <v>23.65220906664505</v>
       </c>
       <c r="H23" t="n">
-        <v>17.90798022314988</v>
+        <v>24.09110944451811</v>
       </c>
       <c r="I23" t="n">
-        <v>0.461308894494703</v>
+        <v>-0.4389003778730611</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0008788043084801786</v>
+        <v>-5.986353328932311e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>17.9071014188414</v>
+        <v>24.09110345816478</v>
       </c>
       <c r="L23" t="n">
-        <v>1.210219652062051</v>
+        <v>2.091623861094936</v>
       </c>
       <c r="M23" t="n">
-        <v>0.03027269616723061</v>
+        <v>1.71007032433174e-05</v>
       </c>
       <c r="N23" t="n">
-        <v>1.562817799482158</v>
+        <v>4.36305313896221</v>
       </c>
       <c r="O23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4201325035470798</v>
+        <v>-0.3034717278511971</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.656396130578626</v>
+        <v>-106.1336367494952</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1766,46 +1770,46 @@
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>17.83827437853432</v>
+        <v>16.80346766296749</v>
       </c>
       <c r="E24" t="n">
-        <v>9.969068960778429</v>
+        <v>16.47057153257236</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>19.51263711882356</v>
+        <v>23.61576106330585</v>
       </c>
       <c r="H24" t="n">
-        <v>20.71651146933186</v>
+        <v>23.94944283080486</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.203874350508304</v>
+        <v>-0.3336817674990051</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.002114968513560345</v>
+        <v>2.377638860297966e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>20.7143965008183</v>
+        <v>23.94946660719346</v>
       </c>
       <c r="L24" t="n">
-        <v>1.216941131041984</v>
+        <v>2.091623860897021</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03699417412281036</v>
+        <v>1.710050532891976e-05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.069001760058768</v>
+        <v>4.295077990601295</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.089388374438732</v>
+        <v>-0.2307393303688046</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.248141655661627</v>
+        <v>-80.69728985674524</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1819,46 +1823,46 @@
         <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.093819670199885</v>
+        <v>19.61369183800984</v>
       </c>
       <c r="E25" t="n">
-        <v>10.78124209171258</v>
+        <v>6.506126959813145</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>10.93571257171925</v>
+        <v>20.36203838638883</v>
       </c>
       <c r="H25" t="n">
-        <v>11.45032524691379</v>
+        <v>21.36636500744163</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5146126751945417</v>
+        <v>-1.004326621052801</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0006204528682394587</v>
+        <v>-7.650292086041966e-07</v>
       </c>
       <c r="K25" t="n">
-        <v>11.45094569978203</v>
+        <v>21.36636424241242</v>
       </c>
       <c r="L25" t="n">
-        <v>1.207047665793013</v>
+        <v>2.091623861014386</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0271007101982832</v>
+        <v>1.710062269329487e-05</v>
       </c>
       <c r="N25" t="n">
-        <v>1.908797951499103</v>
+        <v>3.055381078844222</v>
       </c>
       <c r="O25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4689662282484538</v>
+        <v>-0.6944369961156776</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.129777362718851</v>
+        <v>-242.8670966991942</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1872,46 +1876,46 @@
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.304112753397412</v>
+        <v>-9.330867602360641</v>
       </c>
       <c r="E26" t="n">
-        <v>11.66910645575301</v>
+        <v>0.3059773796144469</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>13.00190760253289</v>
+        <v>8.935378271498534</v>
       </c>
       <c r="H26" t="n">
-        <v>13.3881310820754</v>
+        <v>9.869077073276458</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3862234795425135</v>
+        <v>-0.9336988017779237</v>
       </c>
       <c r="J26" t="n">
-        <v>0.001098186362344066</v>
+        <v>1.919657282905006e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>13.38922926843775</v>
+        <v>9.869096269849287</v>
       </c>
       <c r="L26" t="n">
-        <v>1.208293620710411</v>
+        <v>2.091623860569702</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02834666520357132</v>
+        <v>1.710017800905154e-05</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8661693221638653</v>
+        <v>2.46245197075562</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3523591468881407</v>
+        <v>-0.6456154824391337</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.300492478862957</v>
+        <v>-225.7955687845639</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -1925,46 +1929,46 @@
         <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>-11.00735135144004</v>
+        <v>12.63613614180791</v>
       </c>
       <c r="E27" t="n">
-        <v>5.320278319944421</v>
+        <v>1.069530031619408</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>11.16160479240602</v>
+        <v>13.32528783730165</v>
       </c>
       <c r="H27" t="n">
-        <v>11.79165560199675</v>
+        <v>11.98096368534362</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6300508095907311</v>
+        <v>1.344324151958025</v>
       </c>
       <c r="J27" t="n">
-        <v>0.001480080262353914</v>
+        <v>3.457830111347764e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>11.79313568225911</v>
+        <v>11.98099826364474</v>
       </c>
       <c r="L27" t="n">
-        <v>1.209287581241434</v>
+        <v>2.091623860660242</v>
       </c>
       <c r="M27" t="n">
-        <v>0.02934062667191029</v>
+        <v>1.710026854838563e-05</v>
       </c>
       <c r="N27" t="n">
-        <v>1.724198454459839</v>
+        <v>1.448896172352618</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.5742880791392216</v>
+        <v>0.9295035151390476</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.686887772036486</v>
+        <v>325.0808336999337</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -1978,46 +1982,46 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>-13.8251560104538</v>
+        <v>15.10306711944041</v>
       </c>
       <c r="E28" t="n">
-        <v>-15.2843200875859</v>
+        <v>14.35031542128742</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>20.72254636758528</v>
+        <v>21.2679587631301</v>
       </c>
       <c r="H28" t="n">
-        <v>21.02369152866703</v>
+        <v>20.06963246119449</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3011451610817488</v>
+        <v>1.198326301935612</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00145632268007695</v>
+        <v>3.488136418896494e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>21.02514785134711</v>
+        <v>20.06966734255868</v>
       </c>
       <c r="L28" t="n">
-        <v>1.213568635625783</v>
+        <v>2.091623860804684</v>
       </c>
       <c r="M28" t="n">
-        <v>0.03362167999148369</v>
+        <v>1.710041299121274e-05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.237470422757581</v>
+        <v>2.433063061593341</v>
       </c>
       <c r="O28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.2746874902540672</v>
+        <v>0.8285536906409928</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.65029409618081</v>
+        <v>289.7738228918361</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2031,46 +2035,46 @@
         <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.682845954171761</v>
+        <v>10.2020036471682</v>
       </c>
       <c r="E29" t="n">
-        <v>4.028985546370478</v>
+        <v>22.65732588813449</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>6.8626982209984</v>
+        <v>23.58389669454377</v>
       </c>
       <c r="H29" t="n">
-        <v>7.992588967855227</v>
+        <v>24.93948935432184</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.129890746856827</v>
+        <v>-1.355592659778065</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0005534547239473016</v>
+        <v>6.468212128230253e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>7.993142422579174</v>
+        <v>24.93949582253396</v>
       </c>
       <c r="L29" t="n">
-        <v>1.206210066877766</v>
+        <v>2.091623861071432</v>
       </c>
       <c r="M29" t="n">
-        <v>0.02626311220228672</v>
+        <v>1.710067973875111e-05</v>
       </c>
       <c r="N29" t="n">
-        <v>3.76897472129815</v>
+        <v>4.770218340148596</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>-1.029289769532278</v>
+        <v>-0.9373234600300796</v>
       </c>
       <c r="Q29" t="n">
-        <v>-6.975511055623514</v>
+        <v>-327.8118086821516</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2084,46 +2088,46 @@
         <v>28</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5452164101629293</v>
+        <v>20.65587744102102</v>
       </c>
       <c r="E30" t="n">
-        <v>-12.58571342026514</v>
+        <v>7.776491020567832</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>11.93240846913605</v>
+        <v>21.72455769857014</v>
       </c>
       <c r="H30" t="n">
-        <v>11.71505068494531</v>
+        <v>23.40590207682482</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2173577841907388</v>
+        <v>-1.681344378254675</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0006232915558445584</v>
+        <v>-7.451664490600352e-06</v>
       </c>
       <c r="K30" t="n">
-        <v>11.71442739338947</v>
+        <v>23.40589462516033</v>
       </c>
       <c r="L30" t="n">
-        <v>1.207257583146433</v>
+        <v>2.091623861120983</v>
       </c>
       <c r="M30" t="n">
-        <v>0.02731062844395638</v>
+        <v>1.7100729290428e-05</v>
       </c>
       <c r="N30" t="n">
-        <v>1.767035196335059</v>
+        <v>4.034203889412667</v>
       </c>
       <c r="O30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1983895628717373</v>
+        <v>-1.162553525558616</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.31902478628301</v>
+        <v>-406.5813329290146</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2137,46 +2141,46 @@
         <v>29</v>
       </c>
       <c r="D31" t="n">
-        <v>-15.33826650666168</v>
+        <v>-15.09357680517539</v>
       </c>
       <c r="E31" t="n">
-        <v>-12.23453636512133</v>
+        <v>5.941146935381724</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>21.79081305902023</v>
+        <v>16.89219423778091</v>
       </c>
       <c r="H31" t="n">
-        <v>19.64349702051157</v>
+        <v>16.97240549680293</v>
       </c>
       <c r="I31" t="n">
-        <v>2.147316038508656</v>
+        <v>-0.08021125902202542</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00171654042942321</v>
+        <v>1.661532322441559e-06</v>
       </c>
       <c r="K31" t="n">
-        <v>19.645213560941</v>
+        <v>16.97240715833526</v>
       </c>
       <c r="L31" t="n">
-        <v>1.214036152438734</v>
+        <v>2.09162386092278</v>
       </c>
       <c r="M31" t="n">
-        <v>0.03408919647336006</v>
+        <v>1.710053108646706e-05</v>
       </c>
       <c r="N31" t="n">
-        <v>2.495826992241696</v>
+        <v>0.946608657932272</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.947299933773996</v>
+        <v>-0.05546289510178535</v>
       </c>
       <c r="Q31" t="n">
-        <v>11.62091367173933</v>
+        <v>-19.39722172395433</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2190,46 +2194,46 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>19.06163247574779</v>
+        <v>6.575471258442192</v>
       </c>
       <c r="E32" t="n">
-        <v>-10.68416880801502</v>
+        <v>-15.20326139720933</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>22.47753622783562</v>
+        <v>17.53313906237907</v>
       </c>
       <c r="H32" t="n">
-        <v>21.7709271827303</v>
+        <v>15.63185601287097</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7066090451053171</v>
+        <v>1.901283049508102</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.002604320653975638</v>
+        <v>2.465370433626335e-06</v>
       </c>
       <c r="K32" t="n">
-        <v>21.76832286207633</v>
+        <v>15.6318584782414</v>
       </c>
       <c r="L32" t="n">
-        <v>1.218315482851587</v>
+        <v>2.091623861086726</v>
       </c>
       <c r="M32" t="n">
-        <v>0.03836852684617043</v>
+        <v>1.710069503365765e-05</v>
       </c>
       <c r="N32" t="n">
-        <v>3.634308333156058</v>
+        <v>0.3032450493562161</v>
       </c>
       <c r="O32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.6425353558635232</v>
+        <v>1.31463266596193</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62067327574601</v>
+        <v>459.7686259202045</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2243,46 +2247,46 @@
         <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>-4.997370074282479</v>
+        <v>-10.43474926122941</v>
       </c>
       <c r="E33" t="n">
-        <v>14.21196775710676</v>
+        <v>-14.53206531089718</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>15.9923296266239</v>
+        <v>19.08400082694883</v>
       </c>
       <c r="H33" t="n">
-        <v>14.78722097833781</v>
+        <v>17.08032248516065</v>
       </c>
       <c r="I33" t="n">
-        <v>1.205108648286085</v>
+        <v>2.003678341788181</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0008260796981338049</v>
+        <v>1.437806212819056e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>14.78804705803595</v>
+        <v>17.08033686322278</v>
       </c>
       <c r="L33" t="n">
-        <v>1.208125555147441</v>
+        <v>2.091623860753514</v>
       </c>
       <c r="M33" t="n">
-        <v>0.02817860059440136</v>
+        <v>1.710036182173536e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>0.113977485190787</v>
+        <v>0.9984068846326963</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.095651316055982</v>
+        <v>1.385425234187377</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.174120830412645</v>
+        <v>484.5317468448428</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2296,46 +2300,46 @@
         <v>32</v>
       </c>
       <c r="D34" t="n">
-        <v>-12.22419302303832</v>
+        <v>-9.977079767545661</v>
       </c>
       <c r="E34" t="n">
-        <v>8.643427462128045</v>
+        <v>15.83171377684923</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
       </c>
       <c r="G34" t="n">
-        <v>16.06680638110965</v>
+        <v>20.02131848331578</v>
       </c>
       <c r="H34" t="n">
-        <v>14.40432680101139</v>
+        <v>18.740345883499</v>
       </c>
       <c r="I34" t="n">
-        <v>1.662479580098257</v>
+        <v>1.280972599816778</v>
       </c>
       <c r="J34" t="n">
-        <v>0.001700304956394862</v>
+        <v>1.859114886850341e-05</v>
       </c>
       <c r="K34" t="n">
-        <v>14.40602710596779</v>
+        <v>18.74036447464787</v>
       </c>
       <c r="L34" t="n">
-        <v>1.210566057711584</v>
+        <v>2.091623860768169</v>
       </c>
       <c r="M34" t="n">
-        <v>0.03061910159885883</v>
+        <v>1.710037647647449e-05</v>
       </c>
       <c r="N34" t="n">
-        <v>0.3192956887021487</v>
+        <v>1.795096606004708</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.509446310534682</v>
+        <v>0.8857103983322517</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.491081477989608</v>
+        <v>309.7638270364518</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2349,46 +2353,46 @@
         <v>33</v>
       </c>
       <c r="D35" t="n">
-        <v>10.20128543515487</v>
+        <v>-2.389809673317487</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.178068413328887</v>
+        <v>-3.267060672647943</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
       </c>
       <c r="G35" t="n">
-        <v>9.620911386682685</v>
+        <v>3.520048015196053</v>
       </c>
       <c r="H35" t="n">
-        <v>10.06622391793633</v>
+        <v>6.799016197927813</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4453125312536415</v>
+        <v>-3.27896818273176</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.001686018505170954</v>
+        <v>-2.908978071359814e-05</v>
       </c>
       <c r="K35" t="n">
-        <v>10.06453789943116</v>
+        <v>6.798987108147099</v>
       </c>
       <c r="L35" t="n">
-        <v>1.209345468565752</v>
+        <v>2.091623861022215</v>
       </c>
       <c r="M35" t="n">
-        <v>0.02939851395785809</v>
+        <v>1.710063052214772e-05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.653571864376245</v>
+        <v>3.935875903890682</v>
       </c>
       <c r="O35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.4034059527440121</v>
+        <v>-2.267208994465479</v>
       </c>
       <c r="Q35" t="n">
-        <v>-2.587347836709033</v>
+        <v>-792.9161941757269</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2402,46 +2406,46 @@
         <v>34</v>
       </c>
       <c r="D36" t="n">
-        <v>-12.08492454333855</v>
+        <v>7.607618445038653</v>
       </c>
       <c r="E36" t="n">
-        <v>9.288158609218371</v>
+        <v>8.655796549829175</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
       </c>
       <c r="G36" t="n">
-        <v>16.34718518213844</v>
+        <v>9.959798475767085</v>
       </c>
       <c r="H36" t="n">
-        <v>14.70329581501068</v>
+        <v>10.15203304215709</v>
       </c>
       <c r="I36" t="n">
-        <v>1.643889367127763</v>
+        <v>-0.1922345663900007</v>
       </c>
       <c r="J36" t="n">
-        <v>0.001693970999569829</v>
+        <v>-1.736351845971355e-06</v>
       </c>
       <c r="K36" t="n">
-        <v>14.70498978601025</v>
+        <v>10.15203130580524</v>
       </c>
       <c r="L36" t="n">
-        <v>1.210572788997276</v>
+        <v>2.091623860900894</v>
       </c>
       <c r="M36" t="n">
-        <v>0.03062583319842815</v>
+        <v>1.710050920144499e-05</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1585853475551727</v>
+        <v>2.326664208212584</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.492551675807994</v>
+        <v>-0.1329186023136673</v>
       </c>
       <c r="Q36" t="n">
-        <v>9.383846007210957</v>
+        <v>-46.48609210496662</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2455,46 +2459,46 @@
         <v>35</v>
       </c>
       <c r="D37" t="n">
-        <v>3.610291046092165</v>
+        <v>7.278668947180876</v>
       </c>
       <c r="E37" t="n">
-        <v>3.517944504693787</v>
+        <v>1.444568317684272</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
       </c>
       <c r="G37" t="n">
-        <v>5.953027129629294</v>
+        <v>9.183288422845569</v>
       </c>
       <c r="H37" t="n">
-        <v>7.455013577339173</v>
+        <v>7.992179153679274</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.501986447709879</v>
+        <v>1.191109269166295</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0006734331153687964</v>
+        <v>-9.852318923970921e-08</v>
       </c>
       <c r="K37" t="n">
-        <v>7.454340144223805</v>
+        <v>7.992179055156084</v>
       </c>
       <c r="L37" t="n">
-        <v>1.206202555906473</v>
+        <v>2.091623860879718</v>
       </c>
       <c r="M37" t="n">
-        <v>0.02625560015439987</v>
+        <v>1.71004880245352e-05</v>
       </c>
       <c r="N37" t="n">
-        <v>4.058799802869946</v>
+        <v>3.363232561607703</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>-1.366976747578037</v>
+        <v>0.8235876896021371</v>
       </c>
       <c r="Q37" t="n">
-        <v>-9.265317163490973</v>
+        <v>288.0364090102406</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2508,46 +2512,46 @@
         <v>36</v>
       </c>
       <c r="D38" t="n">
-        <v>17.36321476740133</v>
+        <v>-6.648384777550562</v>
       </c>
       <c r="E38" t="n">
-        <v>1.60154682345275</v>
+        <v>21.0469132918373</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
       </c>
       <c r="G38" t="n">
-        <v>15.67726701992998</v>
+        <v>22.07463887882934</v>
       </c>
       <c r="H38" t="n">
-        <v>16.42292708194032</v>
+        <v>22.42171838653962</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7456600620103355</v>
+        <v>-0.3470795077102835</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.002259618676060143</v>
+        <v>6.739684114262296e-06</v>
       </c>
       <c r="K38" t="n">
-        <v>16.42066746326426</v>
+        <v>22.42172512622374</v>
       </c>
       <c r="L38" t="n">
-        <v>1.215511759418441</v>
+        <v>2.091623861028742</v>
       </c>
       <c r="M38" t="n">
-        <v>0.03556480258703232</v>
+        <v>1.710063704884478e-05</v>
       </c>
       <c r="N38" t="n">
-        <v>0.7631479566870083</v>
+        <v>3.561875767638536</v>
       </c>
       <c r="O38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.6742845882694317</v>
+        <v>-0.239991362949775</v>
       </c>
       <c r="Q38" t="n">
-        <v>-3.941963689515316</v>
+        <v>-83.93271299470122</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2561,46 +2565,46 @@
         <v>37</v>
       </c>
       <c r="D39" t="n">
-        <v>11.3615903860358</v>
+        <v>14.58343516074005</v>
       </c>
       <c r="E39" t="n">
-        <v>-4.484962894586644</v>
+        <v>11.83840025902228</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
       </c>
       <c r="G39" t="n">
-        <v>11.8076696373273</v>
+        <v>20.14013833317198</v>
       </c>
       <c r="H39" t="n">
-        <v>11.17250978028551</v>
+        <v>17.60628164114848</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6351598570417902</v>
+        <v>2.533856692023495</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.001844611126101562</v>
+        <v>3.753908178782041e-05</v>
       </c>
       <c r="K39" t="n">
-        <v>11.17066516915941</v>
+        <v>17.60631918023027</v>
       </c>
       <c r="L39" t="n">
-        <v>1.210266086671202</v>
+        <v>2.091623860755511</v>
       </c>
       <c r="M39" t="n">
-        <v>0.03031913191080093</v>
+        <v>1.710036381799583e-05</v>
       </c>
       <c r="N39" t="n">
-        <v>2.058584004126776</v>
+        <v>1.250839255456144</v>
       </c>
       <c r="O39" t="b">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.5790313082336697</v>
+        <v>1.751998866528004</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.658340267712669</v>
+        <v>612.7353542957369</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2614,46 +2618,99 @@
         <v>38</v>
       </c>
       <c r="D40" t="n">
-        <v>-10.64164059114805</v>
+        <v>-17.65236422260124</v>
       </c>
       <c r="E40" t="n">
-        <v>2.534890400583947</v>
+        <v>5.383529273143424</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
       </c>
       <c r="G40" t="n">
-        <v>10.74450567862613</v>
+        <v>19.93800632331047</v>
       </c>
       <c r="H40" t="n">
-        <v>10.71907444228583</v>
+        <v>20.17813128255079</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02543123634029953</v>
+        <v>-0.2401249592403225</v>
       </c>
       <c r="J40" t="n">
-        <v>0.001376249534298873</v>
+        <v>-4.087455414646992e-06</v>
       </c>
       <c r="K40" t="n">
-        <v>10.72045069182013</v>
+        <v>20.17812719509538</v>
       </c>
       <c r="L40" t="n">
-        <v>1.208854803753612</v>
+        <v>2.091623861154208</v>
       </c>
       <c r="M40" t="n">
-        <v>0.02890784852206707</v>
+        <v>1.710076251502659e-05</v>
       </c>
       <c r="N40" t="n">
-        <v>2.301080800606106</v>
+        <v>2.485115719595274</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.02187852566520973</v>
+        <v>-0.1660305924629088</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1414807112327627</v>
+        <v>-58.06603526654048</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.3682807821820049</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-7.086995656586722</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.20071873308718</v>
+      </c>
+      <c r="H41" t="n">
+        <v>7.855251939817492</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-3.654533206730313</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-3.595858113720316e-05</v>
+      </c>
+      <c r="K41" t="n">
+        <v>7.855215981236355</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.091623861101481</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.710070978835599e-05</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.428964644798262</v>
+      </c>
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-2.526887141303742</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>-883.7319790514944</v>
       </c>
     </row>
   </sheetData>

--- a/history_matching/example/iter2/Cuts/RadiusShouldBe15/train_data.xlsx
+++ b/history_matching/example/iter2/Cuts/RadiusShouldBe15/train_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
   <si>
     <t>Sample_Id</t>
   </si>
@@ -68,127 +68,124 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Data_20180119_074635.000000</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000001</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000002</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000003</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000004</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000005</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000006</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000007</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000008</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000009</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000010</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000011</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000012</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000013</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000014</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000015</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000016</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000017</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000018</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000019</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000020</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000021</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000022</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000023</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000024</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000025</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000026</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000027</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000028</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000029</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000030</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000031</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000032</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000033</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000034</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000035</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000036</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000037</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000038</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000039</t>
+    <t>Data_20180120_214437.000000</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000001</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000002</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000003</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000004</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000005</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000006</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000007</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000008</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000009</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000010</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000011</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000012</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000013</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000014</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000015</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000016</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000017</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000018</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000019</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000020</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000021</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000022</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000023</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000024</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000025</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000026</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000027</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000028</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000029</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000030</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000031</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000032</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000033</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000034</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000035</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000036</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000037</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000038</t>
   </si>
 </sst>
 </file>
@@ -537,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -604,46 +601,46 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.14684535151868</v>
+        <v>0.8497631804685568</v>
       </c>
       <c r="E2" t="n">
-        <v>-19.8468228003866</v>
+        <v>23.73824328809854</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>23.6679788130077</v>
+        <v>24.39657166015621</v>
       </c>
       <c r="H2" t="n">
-        <v>24.18631516111157</v>
+        <v>16.50110373028035</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5183363481038654</v>
+        <v>7.895467929875863</v>
       </c>
       <c r="J2" t="n">
-        <v>5.994731403539465e-06</v>
+        <v>7.17738070090994</v>
       </c>
       <c r="K2" t="n">
-        <v>24.18632115584297</v>
+        <v>23.67848443119028</v>
       </c>
       <c r="L2" t="n">
-        <v>2.091623860877034</v>
+        <v>1.120634907021534</v>
       </c>
       <c r="M2" t="n">
-        <v>1.710048534137996e-05</v>
+        <v>0.411494955130389</v>
       </c>
       <c r="N2" t="n">
-        <v>4.408750548265395</v>
+        <v>4.727026441729921</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3584056881250401</v>
+        <v>0.6783364118144345</v>
       </c>
       <c r="Q2" t="n">
-        <v>-125.346574236864</v>
+        <v>1.119424854701527</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -657,46 +654,46 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.904898148493372</v>
+        <v>-12.02577157496209</v>
       </c>
       <c r="E3" t="n">
-        <v>1.967001998453881</v>
+        <v>7.329832517009407</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>4.638463146816595</v>
+        <v>13.80479329737066</v>
       </c>
       <c r="H3" t="n">
-        <v>6.982382181683306</v>
+        <v>22.18126895820116</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.343919034866711</v>
+        <v>-8.376475660830495</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.680816142548275e-05</v>
+        <v>-8.238030191578028</v>
       </c>
       <c r="K3" t="n">
-        <v>6.982365373521881</v>
+        <v>13.94323876662313</v>
       </c>
       <c r="L3" t="n">
-        <v>2.091623861076854</v>
+        <v>0.7572563208548228</v>
       </c>
       <c r="M3" t="n">
-        <v>1.710068516150588e-05</v>
+        <v>0.04811636896367796</v>
       </c>
       <c r="N3" t="n">
-        <v>3.847867982710427</v>
+        <v>0.6093848456752544</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.620681586275447</v>
+        <v>-0.15909527956367</v>
       </c>
       <c r="Q3" t="n">
-        <v>-566.8037774731993</v>
+        <v>-0.6311496190531332</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -710,46 +707,46 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>10.17802948191527</v>
+        <v>-26.85344877644219</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.083306211143764</v>
+        <v>-8.024554673998978</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>11.36908837759391</v>
+        <v>29.06326999105486</v>
       </c>
       <c r="H4" t="n">
-        <v>11.41550916961251</v>
+        <v>28.52483230863919</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04642079201859595</v>
+        <v>0.5384376824156654</v>
       </c>
       <c r="J4" t="n">
-        <v>1.905459446655853e-05</v>
+        <v>-0.2416613297444609</v>
       </c>
       <c r="K4" t="n">
-        <v>11.41552822420697</v>
+        <v>28.28317097889473</v>
       </c>
       <c r="L4" t="n">
-        <v>2.091623860740872</v>
+        <v>0.7885205401969265</v>
       </c>
       <c r="M4" t="n">
-        <v>1.71003491792033e-05</v>
+        <v>0.07938058830578174</v>
       </c>
       <c r="N4" t="n">
-        <v>1.720279711423503</v>
+        <v>7.620275529726706</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.03211064157189088</v>
+        <v>0.8785029467320795</v>
       </c>
       <c r="Q4" t="n">
-        <v>-11.23022059979408</v>
+        <v>2.768806280118636</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -763,46 +760,46 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>-6.753743942882013</v>
+        <v>-41.51523604339693</v>
       </c>
       <c r="E5" t="n">
-        <v>-22.76013445207743</v>
+        <v>1.695286475258826</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>23.87432497126383</v>
+        <v>41.37719807629199</v>
       </c>
       <c r="H5" t="n">
-        <v>24.35860916701603</v>
+        <v>34.07724451548194</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4842841957521955</v>
+        <v>7.299953560810046</v>
       </c>
       <c r="J5" t="n">
-        <v>1.303124534510539e-05</v>
+        <v>7.111875019460816</v>
       </c>
       <c r="K5" t="n">
-        <v>24.35862219826137</v>
+        <v>41.18911953494276</v>
       </c>
       <c r="L5" t="n">
-        <v>2.091623860987496</v>
+        <v>0.8413302339284994</v>
       </c>
       <c r="M5" t="n">
-        <v>1.710059580287055e-05</v>
+        <v>0.1321902820373546</v>
       </c>
       <c r="N5" t="n">
-        <v>4.491442226666035</v>
+        <v>14.89526373434382</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3348653323305325</v>
+        <v>0.205048218295733</v>
       </c>
       <c r="Q5" t="n">
-        <v>-117.1133384972587</v>
+        <v>0.517296432515206</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -816,46 +813,46 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.189547005439286</v>
+        <v>-0.9279999012154859</v>
       </c>
       <c r="E6" t="n">
-        <v>-15.99828556386437</v>
+        <v>11.59125859863062</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>18.33645025779595</v>
+        <v>11.82669292832045</v>
       </c>
       <c r="H6" t="n">
-        <v>15.4187273154717</v>
+        <v>17.61747641395801</v>
       </c>
       <c r="I6" t="n">
-        <v>2.91772294232425</v>
+        <v>-5.790783485637563</v>
       </c>
       <c r="J6" t="n">
-        <v>3.836161909712691e-06</v>
+        <v>-6.208120920134172</v>
       </c>
       <c r="K6" t="n">
-        <v>15.41873115163361</v>
+        <v>11.40935549382384</v>
       </c>
       <c r="L6" t="n">
-        <v>2.091623860901448</v>
+        <v>0.8146616596663487</v>
       </c>
       <c r="M6" t="n">
-        <v>1.710050975482342e-05</v>
+        <v>0.105521707775204</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2009597926108949</v>
+        <v>2.051073115379237</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.017444915407818</v>
+        <v>0.4623796406890968</v>
       </c>
       <c r="Q6" t="n">
-        <v>705.5681221776304</v>
+        <v>1.284743521413422</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -869,46 +866,46 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.256059070692373</v>
+        <v>14.40102347153904</v>
       </c>
       <c r="E7" t="n">
-        <v>-18.05910606199234</v>
+        <v>-13.78234962365453</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>18.28885081839581</v>
+        <v>21.20510405537468</v>
       </c>
       <c r="H7" t="n">
-        <v>16.80867044993374</v>
+        <v>12.40971992845481</v>
       </c>
       <c r="I7" t="n">
-        <v>1.480180368462069</v>
+        <v>8.795384126919867</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.988268075029135e-05</v>
+        <v>7.728542435354409</v>
       </c>
       <c r="K7" t="n">
-        <v>16.80865056725299</v>
+        <v>20.13826236380922</v>
       </c>
       <c r="L7" t="n">
-        <v>2.091623861080364</v>
+        <v>0.9553807828278872</v>
       </c>
       <c r="M7" t="n">
-        <v>1.710068867076339e-05</v>
+        <v>0.2462408309367424</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8680176802591572</v>
+        <v>2.869964081799136</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.023478395853361</v>
+        <v>1.091469812540261</v>
       </c>
       <c r="Q7" t="n">
-        <v>357.9428348678881</v>
+        <v>2.149908344398389</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -922,46 +919,46 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-13.54903056732685</v>
+        <v>12.05979556706487</v>
       </c>
       <c r="E8" t="n">
-        <v>-17.39727569829309</v>
+        <v>-2.419547785385788</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>21.27033667140947</v>
+        <v>13.60611410555557</v>
       </c>
       <c r="H8" t="n">
-        <v>22.72845973801782</v>
+        <v>12.92951579182733</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.458123066608348</v>
+        <v>0.6765983137282383</v>
       </c>
       <c r="J8" t="n">
-        <v>1.334704803621574e-06</v>
+        <v>-0.4188413031435065</v>
       </c>
       <c r="K8" t="n">
-        <v>22.72846107272262</v>
+        <v>12.51067448868382</v>
       </c>
       <c r="L8" t="n">
-        <v>2.091623860897471</v>
+        <v>0.8461157854318916</v>
       </c>
       <c r="M8" t="n">
-        <v>1.710050577809922e-05</v>
+        <v>0.1369758335407468</v>
       </c>
       <c r="N8" t="n">
-        <v>3.709086196040661</v>
+        <v>1.414728469140952</v>
       </c>
       <c r="O8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.008214140028465</v>
+        <v>1.190895199212767</v>
       </c>
       <c r="Q8" t="n">
-        <v>-352.6063263552313</v>
+        <v>2.959827952250048</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -975,46 +972,46 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>13.89487980954055</v>
+        <v>8.08929013779364</v>
       </c>
       <c r="E9" t="n">
-        <v>-17.70422085822753</v>
+        <v>-5.092869639841126</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>23.1140571947468</v>
+        <v>8.314140081022504</v>
       </c>
       <c r="H9" t="n">
-        <v>24.54498118531205</v>
+        <v>14.59766530853614</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.430923990565255</v>
+        <v>-6.283525227513632</v>
       </c>
       <c r="J9" t="n">
-        <v>1.270842902554682e-05</v>
+        <v>-3.969811025703049</v>
       </c>
       <c r="K9" t="n">
-        <v>24.54499389374108</v>
+        <v>10.62785428283309</v>
       </c>
       <c r="L9" t="n">
-        <v>2.091623860938371</v>
+        <v>0.8310211764725441</v>
       </c>
       <c r="M9" t="n">
-        <v>1.710054667819738e-05</v>
+        <v>0.1218812245813994</v>
       </c>
       <c r="N9" t="n">
-        <v>4.580886771540488</v>
+        <v>2.490848344305753</v>
       </c>
       <c r="O9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9894153147003982</v>
+        <v>-2.538070415818744</v>
       </c>
       <c r="Q9" t="n">
-        <v>-346.031332332813</v>
+        <v>-6.627371377444614</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1028,46 +1025,46 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.32818271504884</v>
+        <v>-35.53491263899764</v>
       </c>
       <c r="E10" t="n">
-        <v>9.479599790308342</v>
+        <v>5.957431075549025</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>14.97282186755557</v>
+        <v>37.41704469074293</v>
       </c>
       <c r="H10" t="n">
-        <v>13.77143818484581</v>
+        <v>31.58656463106522</v>
       </c>
       <c r="I10" t="n">
-        <v>1.201383682709764</v>
+        <v>5.830480059677704</v>
       </c>
       <c r="J10" t="n">
-        <v>1.947224135134614e-05</v>
+        <v>5.349085779516376</v>
       </c>
       <c r="K10" t="n">
-        <v>13.77145765708716</v>
+        <v>36.9356504105816</v>
       </c>
       <c r="L10" t="n">
-        <v>2.091623860615918</v>
+        <v>0.8154139766249702</v>
       </c>
       <c r="M10" t="n">
-        <v>1.710022422562927e-05</v>
+        <v>0.1062740247338255</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5896089017747932</v>
+        <v>12.52869825036848</v>
       </c>
       <c r="O10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8306783586565727</v>
+        <v>0.5331038883046906</v>
       </c>
       <c r="Q10" t="n">
-        <v>290.5184960873896</v>
+        <v>1.476683294070621</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1081,46 +1078,46 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.55346123029825</v>
+        <v>-29.45294621644173</v>
       </c>
       <c r="E11" t="n">
-        <v>8.020785170490411</v>
+        <v>4.946896342389834</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>13.82482571323672</v>
+        <v>30.61111626339154</v>
       </c>
       <c r="H11" t="n">
-        <v>13.12015753563014</v>
+        <v>29.1924940020933</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7046681776065782</v>
+        <v>1.418622261298239</v>
       </c>
       <c r="J11" t="n">
-        <v>1.926403017697167e-05</v>
+        <v>1.453674178829637</v>
       </c>
       <c r="K11" t="n">
-        <v>13.12017679966032</v>
+        <v>30.64616818092294</v>
       </c>
       <c r="L11" t="n">
-        <v>2.091623860596933</v>
+        <v>0.8254393827244841</v>
       </c>
       <c r="M11" t="n">
-        <v>1.710020523995167e-05</v>
+        <v>0.1162994308333394</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9021752478287283</v>
+        <v>8.92183954605713</v>
       </c>
       <c r="O11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.487226602774537</v>
+        <v>-0.03858061873607038</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.4009945532094</v>
+        <v>-0.102783401620764</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1134,46 +1131,46 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>16.04255249472128</v>
+        <v>18.48648211040055</v>
       </c>
       <c r="E12" t="n">
-        <v>2.290772923465952</v>
+        <v>15.29491702411593</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>17.9863059862221</v>
+        <v>24.0180734590077</v>
       </c>
       <c r="H12" t="n">
-        <v>15.7305606089717</v>
+        <v>9.729034004666641</v>
       </c>
       <c r="I12" t="n">
-        <v>2.255745377250399</v>
+        <v>14.28903945434106</v>
       </c>
       <c r="J12" t="n">
-        <v>2.999809046257173e-05</v>
+        <v>14.1454778705834</v>
       </c>
       <c r="K12" t="n">
-        <v>15.73059060706216</v>
+        <v>23.87451187525004</v>
       </c>
       <c r="L12" t="n">
-        <v>2.091623860714704</v>
+        <v>1.241432083767453</v>
       </c>
       <c r="M12" t="n">
-        <v>1.710032301135204e-05</v>
+        <v>0.5322921318763082</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3506291239833654</v>
+        <v>4.749442953673922</v>
       </c>
       <c r="O12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.559705152180395</v>
+        <v>0.1288477259981235</v>
       </c>
       <c r="Q12" t="n">
-        <v>545.4841595779037</v>
+        <v>0.1967719626749498</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1187,46 +1184,46 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.086487760559926</v>
+        <v>-11.92542118768872</v>
       </c>
       <c r="E13" t="n">
-        <v>4.035577394917353</v>
+        <v>10.21862605482636</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>8.425747810866286</v>
+        <v>15.35250593084126</v>
       </c>
       <c r="H13" t="n">
-        <v>8.910522948238849</v>
+        <v>22.05148263996407</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4847751373725639</v>
+        <v>-6.698976709122807</v>
       </c>
       <c r="J13" t="n">
-        <v>1.042458375546595e-05</v>
+        <v>-6.757090791651192</v>
       </c>
       <c r="K13" t="n">
-        <v>8.910533372822606</v>
+        <v>15.29439184831288</v>
       </c>
       <c r="L13" t="n">
-        <v>2.091623860732208</v>
+        <v>0.7671437818060043</v>
       </c>
       <c r="M13" t="n">
-        <v>1.710034051471049e-05</v>
+        <v>0.05800382991485953</v>
       </c>
       <c r="N13" t="n">
-        <v>2.922490829158952</v>
+        <v>0.1694836376615163</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3352029895564081</v>
+        <v>0.06635031686311901</v>
       </c>
       <c r="Q13" t="n">
-        <v>-117.2323033059687</v>
+        <v>0.2412976268181043</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1240,46 +1237,46 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>16.74046363332193</v>
+        <v>0.5013583610587204</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.305734760551586</v>
+        <v>15.70475902611797</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>17.07676913234558</v>
+        <v>15.1563257919741</v>
       </c>
       <c r="H14" t="n">
-        <v>17.57919334559887</v>
+        <v>16.90933288623953</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5024242132532883</v>
+        <v>-1.753007094265429</v>
       </c>
       <c r="J14" t="n">
-        <v>1.978167615422617e-05</v>
+        <v>-2.161049705035424</v>
       </c>
       <c r="K14" t="n">
-        <v>17.57921312727502</v>
+        <v>14.7482831812041</v>
       </c>
       <c r="L14" t="n">
-        <v>2.091623860854852</v>
+        <v>0.8235817455868604</v>
       </c>
       <c r="M14" t="n">
-        <v>1.710046315894872e-05</v>
+        <v>0.1144417936957156</v>
       </c>
       <c r="N14" t="n">
-        <v>1.237830367139244</v>
+        <v>0.1435786449851678</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3474128406391181</v>
+        <v>0.4496267711755336</v>
       </c>
       <c r="Q14" t="n">
-        <v>-121.5020829937273</v>
+        <v>1.206182962205482</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1293,46 +1290,46 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.938798193498763</v>
+        <v>19.99204617787428</v>
       </c>
       <c r="E15" t="n">
-        <v>9.907537890770882</v>
+        <v>-7.046686921402028</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>11.80558237977359</v>
+        <v>21.87083661879726</v>
       </c>
       <c r="H15" t="n">
-        <v>10.92210091302934</v>
+        <v>9.954189175999247</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8834814667442501</v>
+        <v>11.91664744279801</v>
       </c>
       <c r="J15" t="n">
-        <v>1.592090989748252e-06</v>
+        <v>11.67144617081532</v>
       </c>
       <c r="K15" t="n">
-        <v>10.92210250512033</v>
+        <v>21.62563534681457</v>
       </c>
       <c r="L15" t="n">
-        <v>2.091623860891521</v>
+        <v>1.105733519051957</v>
       </c>
       <c r="M15" t="n">
-        <v>1.710049982868096e-05</v>
+        <v>0.3965935671608118</v>
       </c>
       <c r="N15" t="n">
-        <v>1.957087337933492</v>
+        <v>3.616877476747799</v>
       </c>
       <c r="O15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6108785376988971</v>
+        <v>0.2331833199545699</v>
       </c>
       <c r="Q15" t="n">
-        <v>213.6447664685717</v>
+        <v>0.3893587024804507</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1346,46 +1343,46 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>12.83422828743795</v>
+        <v>-17.01004198513147</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.557348754083264</v>
+        <v>-8.052908250234296</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>16.47772549903024</v>
+        <v>18.31428826135992</v>
       </c>
       <c r="H16" t="n">
-        <v>15.76609441820932</v>
+        <v>24.6311408434804</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7116310808209185</v>
+        <v>-6.316852582120475</v>
       </c>
       <c r="J16" t="n">
-        <v>2.44558936171368e-05</v>
+        <v>-5.924211328727773</v>
       </c>
       <c r="K16" t="n">
-        <v>15.76611887410294</v>
+        <v>18.70692951475262</v>
       </c>
       <c r="L16" t="n">
-        <v>2.091623860706821</v>
+        <v>0.8099557250499134</v>
       </c>
       <c r="M16" t="n">
-        <v>1.710031512819588e-05</v>
+        <v>0.1008157731587687</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3676800483026509</v>
+        <v>2.119125887482868</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4920374837539334</v>
+        <v>-0.4362799831143881</v>
       </c>
       <c r="Q16" t="n">
-        <v>172.0829829893228</v>
+        <v>-1.23660695531335</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1399,46 +1396,46 @@
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8019786398993</v>
+        <v>10.41102292794746</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.702548910423928</v>
+        <v>16.89752377037026</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>13.54125036596258</v>
+        <v>18.27964309771316</v>
       </c>
       <c r="H17" t="n">
-        <v>13.09930685887457</v>
+        <v>12.90270250307049</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4419435070880091</v>
+        <v>5.376940594642672</v>
       </c>
       <c r="J17" t="n">
-        <v>2.548479129295552e-05</v>
+        <v>6.009319433953147</v>
       </c>
       <c r="K17" t="n">
-        <v>13.09933234366586</v>
+        <v>18.91202193702363</v>
       </c>
       <c r="L17" t="n">
-        <v>2.091623860679615</v>
+        <v>0.9281885630036332</v>
       </c>
       <c r="M17" t="n">
-        <v>1.710028792246219e-05</v>
+        <v>0.2190486111124885</v>
       </c>
       <c r="N17" t="n">
-        <v>0.912179035542875</v>
+        <v>2.19437805398686</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3055624049874738</v>
+        <v>-0.656385868914391</v>
       </c>
       <c r="Q17" t="n">
-        <v>106.8661102115522</v>
+        <v>-1.351160925184416</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1452,46 +1449,46 @@
         <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.27406783503279</v>
+        <v>2.631698847571798</v>
       </c>
       <c r="E18" t="n">
-        <v>2.761848113869746</v>
+        <v>9.069564194801076</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>15.65036225985333</v>
+        <v>8.956569567739871</v>
       </c>
       <c r="H18" t="n">
-        <v>16.16947542351056</v>
+        <v>16.28129281627229</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5191131636572326</v>
+        <v>-7.324723248532417</v>
       </c>
       <c r="J18" t="n">
-        <v>2.642062974713986e-07</v>
+        <v>-6.36287715343631</v>
       </c>
       <c r="K18" t="n">
-        <v>16.16947568771686</v>
+        <v>9.918415662835978</v>
       </c>
       <c r="L18" t="n">
-        <v>2.091623860909556</v>
+        <v>0.8351394502591418</v>
       </c>
       <c r="M18" t="n">
-        <v>1.710051786312976e-05</v>
+        <v>0.125999498367997</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5612613027475101</v>
+        <v>2.893088628009762</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3589388517041497</v>
+        <v>-1.052509650302216</v>
       </c>
       <c r="Q18" t="n">
-        <v>-125.5329201796075</v>
+        <v>-2.709699792824023</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1505,46 +1502,46 @@
         <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.834730488292834</v>
+        <v>-16.4109885128295</v>
       </c>
       <c r="E19" t="n">
-        <v>-23.01933872568203</v>
+        <v>8.665899695735076</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>23.88169107131525</v>
+        <v>17.76907477084569</v>
       </c>
       <c r="H19" t="n">
-        <v>23.97807877521501</v>
+        <v>23.88841713878718</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.09638770389976159</v>
+        <v>-6.119342367941492</v>
       </c>
       <c r="J19" t="n">
-        <v>5.50018338588372e-06</v>
+        <v>-5.632564562223791</v>
       </c>
       <c r="K19" t="n">
-        <v>23.97808427539839</v>
+        <v>18.25585257656339</v>
       </c>
       <c r="L19" t="n">
-        <v>2.091623860992053</v>
+        <v>0.7649912324854374</v>
       </c>
       <c r="M19" t="n">
-        <v>1.71006003592802e-05</v>
+        <v>0.05585128059429272</v>
       </c>
       <c r="N19" t="n">
-        <v>4.308812341688603</v>
+        <v>1.875088219174687</v>
       </c>
       <c r="O19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.06665068581909565</v>
+        <v>-0.5565478889811644</v>
       </c>
       <c r="Q19" t="n">
-        <v>-23.30991755756904</v>
+        <v>-2.059748527193273</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1558,46 +1555,46 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>9.996879782450131</v>
+        <v>-16.56110675700298</v>
       </c>
       <c r="E20" t="n">
-        <v>-21.96991246467039</v>
+        <v>2.197006845589229</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>25.35433114066483</v>
+        <v>15.44282323516243</v>
       </c>
       <c r="H20" t="n">
-        <v>26.35047027572301</v>
+        <v>24.14376880363312</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9961391350581827</v>
+        <v>-8.700945568470692</v>
       </c>
       <c r="J20" t="n">
-        <v>7.542495059044594e-06</v>
+        <v>-7.571846440983003</v>
       </c>
       <c r="K20" t="n">
-        <v>26.35047781821807</v>
+        <v>16.57192236265012</v>
       </c>
       <c r="L20" t="n">
-        <v>2.091623861029304</v>
+        <v>0.7564443731519787</v>
       </c>
       <c r="M20" t="n">
-        <v>1.710063761129189e-05</v>
+        <v>0.04730442126083396</v>
       </c>
       <c r="N20" t="n">
-        <v>5.447384698872269</v>
+        <v>0.9065766019258013</v>
       </c>
       <c r="O20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6887815366887949</v>
+        <v>-1.298205884744241</v>
       </c>
       <c r="Q20" t="n">
-        <v>-240.8890943976903</v>
+        <v>-5.19136069962778</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1611,46 +1608,46 @@
         <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>-11.06057874938554</v>
+        <v>-13.57908488015537</v>
       </c>
       <c r="E21" t="n">
-        <v>1.579680160257112</v>
+        <v>-4.234143726252498</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>10.93484895637239</v>
+        <v>14.12954167972452</v>
       </c>
       <c r="H21" t="n">
-        <v>11.42697149372634</v>
+        <v>23.1561743099128</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4921225373539517</v>
+        <v>-9.026632630188276</v>
       </c>
       <c r="J21" t="n">
-        <v>1.75090435585368e-05</v>
+        <v>-8.748551245340538</v>
       </c>
       <c r="K21" t="n">
-        <v>11.4269890027699</v>
+        <v>14.40762306457226</v>
       </c>
       <c r="L21" t="n">
-        <v>2.091623860555178</v>
+        <v>0.8003234181125795</v>
       </c>
       <c r="M21" t="n">
-        <v>1.710016348456636e-05</v>
+        <v>0.09118346622143468</v>
       </c>
       <c r="N21" t="n">
-        <v>1.714779390611766</v>
+        <v>0.3391760640898074</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3402882176897832</v>
+        <v>-0.3108416138674381</v>
       </c>
       <c r="Q21" t="n">
-        <v>-119.0114028935219</v>
+        <v>-0.9209029600124341</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1664,46 +1661,46 @@
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.89647450282712</v>
+        <v>15.03625410793309</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.43055333189162</v>
+        <v>-10.47285004820868</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>17.68689301346062</v>
+        <v>17.05142185515759</v>
       </c>
       <c r="H22" t="n">
-        <v>16.82353441609195</v>
+        <v>12.0395688517169</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8633585973686735</v>
+        <v>5.011853003440692</v>
       </c>
       <c r="J22" t="n">
-        <v>5.869554426150801e-06</v>
+        <v>6.355865089013733</v>
       </c>
       <c r="K22" t="n">
-        <v>16.82354028564637</v>
+        <v>18.39543394073063</v>
       </c>
       <c r="L22" t="n">
-        <v>2.091623860734678</v>
+        <v>0.8655707471709406</v>
       </c>
       <c r="M22" t="n">
-        <v>1.710034298441449e-05</v>
+        <v>0.1564307952797958</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8751636370938022</v>
+        <v>1.923651860145534</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5969617045462264</v>
+        <v>-1.444614230575122</v>
       </c>
       <c r="Q22" t="n">
-        <v>208.778539381257</v>
+        <v>-3.39814610285679</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1717,46 +1714,46 @@
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>8.044677671473679</v>
+        <v>-10.08081167242276</v>
       </c>
       <c r="E23" t="n">
-        <v>22.96478865975635</v>
+        <v>14.8457780369409</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>23.65220906664505</v>
+        <v>17.58896809499064</v>
       </c>
       <c r="H23" t="n">
-        <v>24.09110944451811</v>
+        <v>21.16996883478089</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4389003778730611</v>
+        <v>-3.581000739790248</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.986353328932311e-06</v>
+        <v>-3.851054417672895</v>
       </c>
       <c r="K23" t="n">
-        <v>24.09110345816478</v>
+        <v>17.31891441710799</v>
       </c>
       <c r="L23" t="n">
-        <v>2.091623861094936</v>
+        <v>0.822648335136244</v>
       </c>
       <c r="M23" t="n">
-        <v>1.71007032433174e-05</v>
+        <v>0.1135083832450992</v>
       </c>
       <c r="N23" t="n">
-        <v>4.36305313896221</v>
+        <v>1.3229038843248</v>
       </c>
       <c r="O23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3034717278511971</v>
+        <v>0.29774397685911</v>
       </c>
       <c r="Q23" t="n">
-        <v>-106.1336367494952</v>
+        <v>0.8015601676260128</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1770,46 +1767,46 @@
         <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>16.80346766296749</v>
+        <v>-14.43425957086176</v>
       </c>
       <c r="E24" t="n">
-        <v>16.47057153257236</v>
+        <v>3.052652185257472</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>23.61576106330585</v>
+        <v>15.54489676727618</v>
       </c>
       <c r="H24" t="n">
-        <v>23.94944283080486</v>
+        <v>23.27203251751863</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3336817674990051</v>
+        <v>-7.727135750242452</v>
       </c>
       <c r="J24" t="n">
-        <v>2.377638860297966e-05</v>
+        <v>-8.544821794160377</v>
       </c>
       <c r="K24" t="n">
-        <v>23.94946660719346</v>
+        <v>14.72721072335825</v>
       </c>
       <c r="L24" t="n">
-        <v>2.091623860897021</v>
+        <v>0.7575917872113231</v>
       </c>
       <c r="M24" t="n">
-        <v>1.710050532891976e-05</v>
+        <v>0.04845183532017837</v>
       </c>
       <c r="N24" t="n">
-        <v>4.295077990601295</v>
+        <v>0.1572960616843289</v>
       </c>
       <c r="O24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2307393303688046</v>
+        <v>0.9394398020905897</v>
       </c>
       <c r="Q24" t="n">
-        <v>-80.69728985674524</v>
+        <v>3.714766061610799</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1823,46 +1820,46 @@
         <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>19.61369183800984</v>
+        <v>-41.90001253276814</v>
       </c>
       <c r="E25" t="n">
-        <v>6.506126959813145</v>
+        <v>4.380172249458369</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>20.36203838638883</v>
+        <v>42.48642379401265</v>
       </c>
       <c r="H25" t="n">
-        <v>21.36636500744163</v>
+        <v>34.1617210879232</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.004326621052801</v>
+        <v>8.324702706089447</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.650292086041966e-07</v>
+        <v>7.71611686333596</v>
       </c>
       <c r="K25" t="n">
-        <v>21.36636424241242</v>
+        <v>41.87783795125917</v>
       </c>
       <c r="L25" t="n">
-        <v>2.091623861014386</v>
+        <v>0.8538725285180989</v>
       </c>
       <c r="M25" t="n">
-        <v>1.710062269329487e-05</v>
+        <v>0.1447325766269541</v>
       </c>
       <c r="N25" t="n">
-        <v>3.055381078844222</v>
+        <v>15.25606016129792</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6944369961156776</v>
+        <v>0.6586054568156727</v>
       </c>
       <c r="Q25" t="n">
-        <v>-242.8670966991942</v>
+        <v>1.59970056598285</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1876,46 +1873,46 @@
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.330867602360641</v>
+        <v>-15.23491735759201</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3059773796144469</v>
+        <v>3.800184448019621</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>8.935378271498534</v>
+        <v>15.91015344265877</v>
       </c>
       <c r="H26" t="n">
-        <v>9.869077073276458</v>
+        <v>23.56769073083086</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9336988017779237</v>
+        <v>-7.657537288172096</v>
       </c>
       <c r="J26" t="n">
-        <v>1.919657282905006e-05</v>
+        <v>-7.992985881690684</v>
       </c>
       <c r="K26" t="n">
-        <v>9.869096269849287</v>
+        <v>15.57470484914018</v>
       </c>
       <c r="L26" t="n">
-        <v>2.091623860569702</v>
+        <v>0.7526315906879041</v>
       </c>
       <c r="M26" t="n">
-        <v>1.710017800905154e-05</v>
+        <v>0.0434916387967594</v>
       </c>
       <c r="N26" t="n">
-        <v>2.46245197075562</v>
+        <v>0.3316605654329656</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.6456154824391337</v>
+        <v>0.3866649030448182</v>
       </c>
       <c r="Q26" t="n">
-        <v>-225.7955687845639</v>
+        <v>1.608507495574106</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -1929,46 +1926,46 @@
         <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>12.63613614180791</v>
+        <v>-39.36137950218873</v>
       </c>
       <c r="E27" t="n">
-        <v>1.069530031619408</v>
+        <v>6.961533245122182</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>13.32528783730165</v>
+        <v>39.75574010138832</v>
       </c>
       <c r="H27" t="n">
-        <v>11.98096368534362</v>
+        <v>33.08440182216528</v>
       </c>
       <c r="I27" t="n">
-        <v>1.344324151958025</v>
+        <v>6.671338279223036</v>
       </c>
       <c r="J27" t="n">
-        <v>3.457830111347764e-05</v>
+        <v>7.386933570962932</v>
       </c>
       <c r="K27" t="n">
-        <v>11.98099826364474</v>
+        <v>40.47133539312821</v>
       </c>
       <c r="L27" t="n">
-        <v>2.091623860660242</v>
+        <v>0.8718056778036118</v>
       </c>
       <c r="M27" t="n">
-        <v>1.710026854838563e-05</v>
+        <v>0.1626657259124671</v>
       </c>
       <c r="N27" t="n">
-        <v>1.448896172352618</v>
+        <v>14.41613303349885</v>
       </c>
       <c r="O27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9295035151390476</v>
+        <v>-0.7664037620596295</v>
       </c>
       <c r="Q27" t="n">
-        <v>325.0808336999337</v>
+        <v>-1.774268926592203</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -1982,46 +1979,46 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>15.10306711944041</v>
+        <v>-0.03259009239693</v>
       </c>
       <c r="E28" t="n">
-        <v>14.35031542128742</v>
+        <v>-10.10950871589915</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>21.2679587631301</v>
+        <v>11.20376454891801</v>
       </c>
       <c r="H28" t="n">
-        <v>20.06963246119449</v>
+        <v>17.98258443617823</v>
       </c>
       <c r="I28" t="n">
-        <v>1.198326301935612</v>
+        <v>-6.778819887260223</v>
       </c>
       <c r="J28" t="n">
-        <v>3.488136418896494e-05</v>
+        <v>-6.806928443157709</v>
       </c>
       <c r="K28" t="n">
-        <v>20.06966734255868</v>
+        <v>11.17565599302052</v>
       </c>
       <c r="L28" t="n">
-        <v>2.091623860804684</v>
+        <v>0.8683245957292429</v>
       </c>
       <c r="M28" t="n">
-        <v>1.710041299121274e-05</v>
+        <v>0.1591846438380981</v>
       </c>
       <c r="N28" t="n">
-        <v>2.433063061593341</v>
+        <v>2.165689998332216</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8285536906409928</v>
+        <v>0.03016459387464196</v>
       </c>
       <c r="Q28" t="n">
-        <v>289.7738228918361</v>
+        <v>0.07045112764945585</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2035,46 +2032,46 @@
         <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>10.2020036471682</v>
+        <v>-31.92573329309284</v>
       </c>
       <c r="E29" t="n">
-        <v>22.65732588813449</v>
+        <v>-12.75102662144095</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>23.58389669454377</v>
+        <v>34.05021306630596</v>
       </c>
       <c r="H29" t="n">
-        <v>24.93948935432184</v>
+        <v>30.66098178630929</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.355592659778065</v>
+        <v>3.389231279996668</v>
       </c>
       <c r="J29" t="n">
-        <v>6.468212128230253e-06</v>
+        <v>3.701790338510815</v>
       </c>
       <c r="K29" t="n">
-        <v>24.93949582253396</v>
+        <v>34.3627721248201</v>
       </c>
       <c r="L29" t="n">
-        <v>2.091623861071432</v>
+        <v>0.9739917662301871</v>
       </c>
       <c r="M29" t="n">
-        <v>1.710067973875111e-05</v>
+        <v>0.2648518143390424</v>
       </c>
       <c r="N29" t="n">
-        <v>4.770218340148596</v>
+        <v>10.78376890483262</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.9373234600300796</v>
+        <v>-0.3167046553627546</v>
       </c>
       <c r="Q29" t="n">
-        <v>-327.8118086821516</v>
+        <v>-0.6073382222051207</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -2088,46 +2085,46 @@
         <v>28</v>
       </c>
       <c r="D30" t="n">
-        <v>20.65587744102102</v>
+        <v>14.08712021271873</v>
       </c>
       <c r="E30" t="n">
-        <v>7.776491020567832</v>
+        <v>0.5474653959434335</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>21.72455769857014</v>
+        <v>14.88883877769784</v>
       </c>
       <c r="H30" t="n">
-        <v>23.40590207682482</v>
+        <v>12.01867463620344</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.681344378254675</v>
+        <v>2.870164141494401</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.451664490600352e-06</v>
+        <v>1.896935657875835</v>
       </c>
       <c r="K30" t="n">
-        <v>23.40589462516033</v>
+        <v>13.91561029407927</v>
       </c>
       <c r="L30" t="n">
-        <v>2.091623861120983</v>
+        <v>0.8811823149961984</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7100729290428e-05</v>
+        <v>0.1720423631050537</v>
       </c>
       <c r="N30" t="n">
-        <v>4.034203889412667</v>
+        <v>0.6128175701157156</v>
       </c>
       <c r="O30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-1.162553525558616</v>
+        <v>1.036768813137057</v>
       </c>
       <c r="Q30" t="n">
-        <v>-406.5813329290146</v>
+        <v>2.346373318075927</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2141,46 +2138,46 @@
         <v>29</v>
       </c>
       <c r="D31" t="n">
-        <v>-15.09357680517539</v>
+        <v>-19.59977597091169</v>
       </c>
       <c r="E31" t="n">
-        <v>5.941146935381724</v>
+        <v>7.802351578417416</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>16.89219423778091</v>
+        <v>21.21903935697876</v>
       </c>
       <c r="H31" t="n">
-        <v>16.97240549680293</v>
+        <v>25.1855887027344</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.08021125902202542</v>
+        <v>-3.966549345755634</v>
       </c>
       <c r="J31" t="n">
-        <v>1.661532322441559e-06</v>
+        <v>-4.188886446949054</v>
       </c>
       <c r="K31" t="n">
-        <v>16.97240715833526</v>
+        <v>20.99670225578534</v>
       </c>
       <c r="L31" t="n">
-        <v>2.09162386092278</v>
+        <v>0.7772848372496959</v>
       </c>
       <c r="M31" t="n">
-        <v>1.710053108646706e-05</v>
+        <v>0.06814488535855118</v>
       </c>
       <c r="N31" t="n">
-        <v>0.946608657932272</v>
+        <v>3.446559998964685</v>
       </c>
       <c r="O31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.05546289510178535</v>
+        <v>0.2521865039820013</v>
       </c>
       <c r="Q31" t="n">
-        <v>-19.39722172395433</v>
+        <v>0.8517169818442841</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2194,46 +2191,46 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>6.575471258442192</v>
+        <v>9.051791998093172</v>
       </c>
       <c r="E32" t="n">
-        <v>-15.20326139720933</v>
+        <v>-16.17092341658406</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>17.53313906237907</v>
+        <v>18.07399724949116</v>
       </c>
       <c r="H32" t="n">
-        <v>15.63185601287097</v>
+        <v>14.60398936889539</v>
       </c>
       <c r="I32" t="n">
-        <v>1.901283049508102</v>
+        <v>3.470007880595766</v>
       </c>
       <c r="J32" t="n">
-        <v>2.465370433626335e-06</v>
+        <v>3.945982500118754</v>
       </c>
       <c r="K32" t="n">
-        <v>15.6318584782414</v>
+        <v>18.54997186901415</v>
       </c>
       <c r="L32" t="n">
-        <v>2.091623861086726</v>
+        <v>1.000218133591814</v>
       </c>
       <c r="M32" t="n">
-        <v>1.710069503365765e-05</v>
+        <v>0.2910781817006689</v>
       </c>
       <c r="N32" t="n">
-        <v>0.3032450493562161</v>
+        <v>1.969104012255602</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.31463266596193</v>
+        <v>-0.47592271498774</v>
       </c>
       <c r="Q32" t="n">
-        <v>459.7686259202045</v>
+        <v>-0.8822242043161123</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2247,46 +2244,46 @@
         <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>-10.43474926122941</v>
+        <v>-24.24404167657215</v>
       </c>
       <c r="E33" t="n">
-        <v>-14.53206531089718</v>
+        <v>-6.301145860923412</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>19.08400082694883</v>
+        <v>26.06599532052696</v>
       </c>
       <c r="H33" t="n">
-        <v>17.08032248516065</v>
+        <v>27.442806191195</v>
       </c>
       <c r="I33" t="n">
-        <v>2.003678341788181</v>
+        <v>-1.376810870668045</v>
       </c>
       <c r="J33" t="n">
-        <v>1.437806212819056e-05</v>
+        <v>-2.255401178324887</v>
       </c>
       <c r="K33" t="n">
-        <v>17.08033686322278</v>
+        <v>25.18740501287012</v>
       </c>
       <c r="L33" t="n">
-        <v>2.091623860753514</v>
+        <v>0.7838579889957232</v>
       </c>
       <c r="M33" t="n">
-        <v>1.710036182173536e-05</v>
+        <v>0.07471803710457847</v>
       </c>
       <c r="N33" t="n">
-        <v>0.9984068846326963</v>
+        <v>5.848788922294259</v>
       </c>
       <c r="O33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>1.385425234187377</v>
+        <v>0.9923564880332937</v>
       </c>
       <c r="Q33" t="n">
-        <v>484.5317468448428</v>
+        <v>3.214205803241582</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2300,46 +2297,46 @@
         <v>32</v>
       </c>
       <c r="D34" t="n">
-        <v>-9.977079767545661</v>
+        <v>2.862106452276294</v>
       </c>
       <c r="E34" t="n">
-        <v>15.83171377684923</v>
+        <v>-13.81109939610121</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
       </c>
       <c r="G34" t="n">
-        <v>20.02131848331578</v>
+        <v>15.64820377908749</v>
       </c>
       <c r="H34" t="n">
-        <v>18.740345883499</v>
+        <v>16.96368468434586</v>
       </c>
       <c r="I34" t="n">
-        <v>1.280972599816778</v>
+        <v>-1.315480905258374</v>
       </c>
       <c r="J34" t="n">
-        <v>1.859114886850341e-05</v>
+        <v>-2.715586749200659</v>
       </c>
       <c r="K34" t="n">
-        <v>18.74036447464787</v>
+        <v>14.24809793514521</v>
       </c>
       <c r="L34" t="n">
-        <v>2.091623860768169</v>
+        <v>0.9183460673986158</v>
       </c>
       <c r="M34" t="n">
-        <v>1.710037647647449e-05</v>
+        <v>0.209206115507471</v>
       </c>
       <c r="N34" t="n">
-        <v>1.795096606004708</v>
+        <v>0.4224204856103533</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8857103983322517</v>
+        <v>1.46102512012782</v>
       </c>
       <c r="Q34" t="n">
-        <v>309.7638270364518</v>
+        <v>3.061072956167257</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2353,46 +2350,46 @@
         <v>33</v>
       </c>
       <c r="D35" t="n">
-        <v>-2.389809673317487</v>
+        <v>-38.73014971641683</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.267060672647943</v>
+        <v>-5.842758186235869</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
       </c>
       <c r="G35" t="n">
-        <v>3.520048015196053</v>
+        <v>38.298758685184</v>
       </c>
       <c r="H35" t="n">
-        <v>6.799016197927813</v>
+        <v>33.16693251176258</v>
       </c>
       <c r="I35" t="n">
-        <v>-3.27896818273176</v>
+        <v>5.131826173421416</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.908978071359814e-05</v>
+        <v>5.565145921139748</v>
       </c>
       <c r="K35" t="n">
-        <v>6.798987108147099</v>
+        <v>38.73207843290233</v>
       </c>
       <c r="L35" t="n">
-        <v>2.091623861022215</v>
+        <v>0.9902958566699473</v>
       </c>
       <c r="M35" t="n">
-        <v>1.710063052214772e-05</v>
+        <v>0.2811559047788026</v>
       </c>
       <c r="N35" t="n">
-        <v>3.935875903890682</v>
+        <v>13.18388609673612</v>
       </c>
       <c r="O35" t="b">
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>-2.267208994465479</v>
+        <v>-0.4354376732037039</v>
       </c>
       <c r="Q35" t="n">
-        <v>-792.9161941757269</v>
+        <v>-0.81721226711503</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2406,46 +2403,46 @@
         <v>34</v>
       </c>
       <c r="D36" t="n">
-        <v>7.607618445038653</v>
+        <v>-23.0117549770495</v>
       </c>
       <c r="E36" t="n">
-        <v>8.655796549829175</v>
+        <v>-14.86805480118175</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
       </c>
       <c r="G36" t="n">
-        <v>9.959798475767085</v>
+        <v>27.26949600921141</v>
       </c>
       <c r="H36" t="n">
-        <v>10.15203304215709</v>
+        <v>27.20344849018714</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1922345663900007</v>
+        <v>0.06604751902426642</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.736351845971355e-06</v>
+        <v>0.3634249750326419</v>
       </c>
       <c r="K36" t="n">
-        <v>10.15203130580524</v>
+        <v>27.56687346521979</v>
       </c>
       <c r="L36" t="n">
-        <v>2.091623860900894</v>
+        <v>1.0194884913312</v>
       </c>
       <c r="M36" t="n">
-        <v>1.710050920144499e-05</v>
+        <v>0.310348539440055</v>
       </c>
       <c r="N36" t="n">
-        <v>2.326664208212584</v>
+        <v>6.950040506038154</v>
       </c>
       <c r="O36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.1329186023136673</v>
+        <v>-0.294521414829112</v>
       </c>
       <c r="Q36" t="n">
-        <v>-46.48609210496662</v>
+        <v>-0.5338056779172046</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2459,46 +2456,46 @@
         <v>35</v>
       </c>
       <c r="D37" t="n">
-        <v>7.278668947180876</v>
+        <v>-7.586088859036651</v>
       </c>
       <c r="E37" t="n">
-        <v>1.444568317684272</v>
+        <v>19.73636498681199</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
       </c>
       <c r="G37" t="n">
-        <v>9.183288422845569</v>
+        <v>20.18005974625354</v>
       </c>
       <c r="H37" t="n">
-        <v>7.992179153679274</v>
+        <v>20.01632233282904</v>
       </c>
       <c r="I37" t="n">
-        <v>1.191109269166295</v>
+        <v>0.1637374134244958</v>
       </c>
       <c r="J37" t="n">
-        <v>-9.852318923970921e-08</v>
+        <v>0.6890717030258118</v>
       </c>
       <c r="K37" t="n">
-        <v>7.992179055156084</v>
+        <v>20.70539403585486</v>
       </c>
       <c r="L37" t="n">
-        <v>2.091623860879718</v>
+        <v>0.9535912030324213</v>
       </c>
       <c r="M37" t="n">
-        <v>1.71004880245352e-05</v>
+        <v>0.2444512511412766</v>
       </c>
       <c r="N37" t="n">
-        <v>3.363232561607703</v>
+        <v>3.187624070130763</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8235876896021371</v>
+        <v>-0.5379657551056442</v>
       </c>
       <c r="Q37" t="n">
-        <v>288.0364090102406</v>
+        <v>-1.062526124165267</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2512,46 +2509,46 @@
         <v>36</v>
       </c>
       <c r="D38" t="n">
-        <v>-6.648384777550562</v>
+        <v>8.73789248003942</v>
       </c>
       <c r="E38" t="n">
-        <v>21.0469132918373</v>
+        <v>8.200762284205453</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
       </c>
       <c r="G38" t="n">
-        <v>22.07463887882934</v>
+        <v>11.58475745145461</v>
       </c>
       <c r="H38" t="n">
-        <v>22.42171838653962</v>
+        <v>13.8762732850157</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3470795077102835</v>
+        <v>-2.291515833561085</v>
       </c>
       <c r="J38" t="n">
-        <v>6.739684114262296e-06</v>
+        <v>-2.190887277350168</v>
       </c>
       <c r="K38" t="n">
-        <v>22.42172512622374</v>
+        <v>11.68538600766553</v>
       </c>
       <c r="L38" t="n">
-        <v>2.091623861028742</v>
+        <v>0.8518659426375806</v>
       </c>
       <c r="M38" t="n">
-        <v>1.710063704884478e-05</v>
+        <v>0.1427259907464359</v>
       </c>
       <c r="N38" t="n">
-        <v>3.561875767638536</v>
+        <v>1.882007921851817</v>
       </c>
       <c r="O38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.239991362949775</v>
+        <v>-0.1090273895313992</v>
       </c>
       <c r="Q38" t="n">
-        <v>-83.93271299470122</v>
+        <v>-0.2663604306653792</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2565,46 +2562,46 @@
         <v>37</v>
       </c>
       <c r="D39" t="n">
-        <v>14.58343516074005</v>
+        <v>-40.23807994927729</v>
       </c>
       <c r="E39" t="n">
-        <v>11.83840025902228</v>
+        <v>3.977584805922135</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
       </c>
       <c r="G39" t="n">
-        <v>20.14013833317198</v>
+        <v>40.1961231578856</v>
       </c>
       <c r="H39" t="n">
-        <v>17.60628164114848</v>
+        <v>33.51072428031452</v>
       </c>
       <c r="I39" t="n">
-        <v>2.533856692023495</v>
+        <v>6.685398877571082</v>
       </c>
       <c r="J39" t="n">
-        <v>3.753908178782041e-05</v>
+        <v>7.053465594606978</v>
       </c>
       <c r="K39" t="n">
-        <v>17.60631918023027</v>
+        <v>40.5641898749215</v>
       </c>
       <c r="L39" t="n">
-        <v>2.091623860755511</v>
+        <v>0.7811509699982551</v>
       </c>
       <c r="M39" t="n">
-        <v>1.710036381799583e-05</v>
+        <v>0.07201101810711034</v>
       </c>
       <c r="N39" t="n">
-        <v>1.250839255456144</v>
+        <v>14.68345480524913</v>
       </c>
       <c r="O39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>1.751998866528004</v>
+        <v>-0.4164463493456408</v>
       </c>
       <c r="Q39" t="n">
-        <v>612.7353542957369</v>
+        <v>-1.371598722554615</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2618,99 +2615,46 @@
         <v>38</v>
       </c>
       <c r="D40" t="n">
-        <v>-17.65236422260124</v>
+        <v>6.735783985791046</v>
       </c>
       <c r="E40" t="n">
-        <v>5.383529273143424</v>
+        <v>-6.521797213862925</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
       </c>
       <c r="G40" t="n">
-        <v>19.93800632331047</v>
+        <v>10.44754326885495</v>
       </c>
       <c r="H40" t="n">
-        <v>20.17813128255079</v>
+        <v>15.18330677431225</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2401249592403225</v>
+        <v>-4.7357635054573</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.087455414646992e-06</v>
+        <v>-4.622835826710745</v>
       </c>
       <c r="K40" t="n">
-        <v>20.17812719509538</v>
+        <v>10.56047094760151</v>
       </c>
       <c r="L40" t="n">
-        <v>2.091623861154208</v>
+        <v>0.8292150120516643</v>
       </c>
       <c r="M40" t="n">
-        <v>1.710076251502659e-05</v>
+        <v>0.1200750601605195</v>
       </c>
       <c r="N40" t="n">
-        <v>2.485115719595274</v>
+        <v>2.529978873720552</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.1660305924629088</v>
+        <v>-0.1240128885208572</v>
       </c>
       <c r="Q40" t="n">
-        <v>-58.06603526654048</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
-      <c r="A41" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="C41" t="n">
-        <v>39</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-0.3682807821820049</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-7.086995656586722</v>
-      </c>
-      <c r="F41" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" t="n">
-        <v>4.20071873308718</v>
-      </c>
-      <c r="H41" t="n">
-        <v>7.855251939817492</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-3.654533206730313</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-3.595858113720316e-05</v>
-      </c>
-      <c r="K41" t="n">
-        <v>7.855215981236355</v>
-      </c>
-      <c r="L41" t="n">
-        <v>2.091623861101481</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.710070978835599e-05</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.428964644798262</v>
-      </c>
-      <c r="O41" t="b">
-        <v>1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>-2.526887141303742</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>-883.7319790514944</v>
+        <v>-0.3258922215394241</v>
       </c>
     </row>
   </sheetData>
